--- a/administrative_forms/009_lockout_tagout_safety_assessment--administrative_forms.xlsx
+++ b/administrative_forms/009_lockout_tagout_safety_assessment--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Potential Hazards</t>
+          <t>Potential Hazards Page 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>lockout_tagout_safety_hazard_page</t>
+          <t>lockout_tagout_safety_hazard_page_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>equipment_lockout_tagout_page</t>
+          <t>equipment_lockout_tagout_page_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Equipment Lockout/Tagout</t>
+          <t>Equipment Lockout Tagout Page 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>personnel_lockout_tagout_page</t>
+          <t>personnel_lockout_tagout_page_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Personnel Lockout/Tagout</t>
+          <t>Personnel Lockout Tagout Page 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>procedures_lockout_tagout_page</t>
+          <t>procedures_lockout_tagout_page_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Procedures Lockout/Tagout</t>
+          <t>Procedures Lockout Tagout Page 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
